--- a/public/crawlability-amosziv-september-2026.xlsx
+++ b/public/crawlability-amosziv-september-2026.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להסיר 1 רשומות כפולות ממפת האתר.</t>
+          <t>להסיר רשומה כפולה אחת ממפת האתר.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>שגיאות שכבר תוקנו</t>
+          <t>כתובות שדווחו כשגיאה ומחזירות 200 כיום</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">

--- a/public/crawlability-amosziv-september-2026.xlsx
+++ b/public/crawlability-amosziv-september-2026.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://www.amosziv.co.il/טיפול-ביתי/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://www.amosziv.co.il/privacy-policy, 348 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://www.amosziv.co.il/privacy-policy, 348 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://www.amosziv.co.il/טיפול-ביתי/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">

--- a/public/crawlability-amosziv-september-2026.xlsx
+++ b/public/crawlability-amosziv-september-2026.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">

--- a/public/crawlability-amosziv-september-2026.xlsx
+++ b/public/crawlability-amosziv-september-2026.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://www.amosziv.co.il/privacy-policy, 348 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות; הבולטת https://www.amosziv.co.il/privacy-policy (348 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://www.amosziv.co.il/טיפול-ביתי/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://www.amosziv.co.il/טיפול-ביתי/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-amosziv-september-2026.xlsx
+++ b/public/crawlability-amosziv-september-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -515,21 +515,6 @@
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>להסיר רשומה כפולה אחת ממפת האתר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://www.amosziv.co.il/טיפול-ביתי/ (קישור נכנס אחד).</t>
         </is>
